--- a/data/Ficha_25_DL1153_202605_EsperaAtrencion_Referido.xlsx
+++ b/data/Ficha_25_DL1153_202605_EsperaAtrencion_Referido.xlsx
@@ -226,10 +226,10 @@
     <t>Logro Esperado:</t>
   </si>
   <si>
-    <t>FUENTE: Refcon: 11/05/2026</t>
-  </si>
-  <si>
     <t>PERIODO: ENERO - MAYO 2026</t>
+  </si>
+  <si>
+    <t>FUENTE: Refcon: 25/05/2026</t>
   </si>
 </sst>
 </file>
@@ -722,7 +722,7 @@
 </file>
 
 <file path=xl/pivotCache/pivotCacheDefinition1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1" refreshedBy="TuSoft" refreshedDate="46160.52405821759" createdVersion="6" refreshedVersion="6" minRefreshableVersion="3" recordCount="66">
+<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1" refreshedBy="TuSoft" refreshedDate="46167.527127083333" createdVersion="6" refreshedVersion="6" minRefreshableVersion="3" recordCount="66">
   <cacheSource type="worksheet">
     <worksheetSource name="Tabla1"/>
   </cacheSource>
@@ -884,8 +884,8 @@
     <x v="0"/>
     <x v="0"/>
     <n v="3879"/>
-    <n v="4"/>
-    <n v="0"/>
+    <n v="14"/>
+    <n v="2"/>
   </r>
   <r>
     <x v="0"/>
@@ -954,7 +954,7 @@
     <x v="0"/>
     <x v="1"/>
     <n v="3899"/>
-    <n v="5"/>
+    <n v="9"/>
     <n v="8"/>
   </r>
   <r>
@@ -1024,8 +1024,8 @@
     <x v="1"/>
     <x v="2"/>
     <n v="3917"/>
-    <n v="27"/>
-    <n v="14"/>
+    <n v="76"/>
+    <n v="81"/>
   </r>
   <r>
     <x v="0"/>
@@ -1094,8 +1094,8 @@
     <x v="0"/>
     <x v="3"/>
     <n v="3930"/>
-    <n v="6"/>
-    <n v="3"/>
+    <n v="65"/>
+    <n v="216"/>
   </r>
   <r>
     <x v="0"/>
@@ -1164,8 +1164,8 @@
     <x v="1"/>
     <x v="4"/>
     <n v="3943"/>
-    <n v="71"/>
-    <n v="62"/>
+    <n v="156"/>
+    <n v="123"/>
   </r>
   <r>
     <x v="0"/>
@@ -1234,8 +1234,8 @@
     <x v="0"/>
     <x v="5"/>
     <n v="3976"/>
-    <n v="27"/>
-    <n v="214"/>
+    <n v="61"/>
+    <n v="318"/>
   </r>
   <r>
     <x v="0"/>
@@ -1304,8 +1304,8 @@
     <x v="0"/>
     <x v="6"/>
     <n v="3989"/>
+    <n v="17"/>
     <n v="9"/>
-    <n v="4"/>
   </r>
   <r>
     <x v="0"/>
@@ -1402,8 +1402,8 @@
     <x v="1"/>
     <x v="8"/>
     <n v="4074"/>
-    <n v="67"/>
-    <n v="524"/>
+    <n v="142"/>
+    <n v="1239"/>
   </r>
   <r>
     <x v="0"/>
@@ -1472,8 +1472,8 @@
     <x v="0"/>
     <x v="9"/>
     <n v="4083"/>
-    <n v="2"/>
-    <n v="0"/>
+    <n v="4"/>
+    <n v="6"/>
   </r>
   <r>
     <x v="0"/>
@@ -1528,8 +1528,8 @@
     <x v="0"/>
     <x v="10"/>
     <n v="4090"/>
-    <n v="1"/>
     <n v="14"/>
+    <n v="21"/>
   </r>
   <r>
     <x v="0"/>
@@ -1598,8 +1598,8 @@
     <x v="0"/>
     <x v="11"/>
     <n v="4128"/>
-    <n v="1"/>
     <n v="8"/>
+    <n v="21"/>
   </r>
   <r>
     <x v="0"/>
@@ -1668,8 +1668,8 @@
     <x v="2"/>
     <x v="12"/>
     <n v="3853"/>
-    <n v="496"/>
-    <n v="1191"/>
+    <n v="1320"/>
+    <n v="2131"/>
   </r>
   <r>
     <x v="0"/>
@@ -1738,7 +1738,7 @@
     <x v="0"/>
     <x v="13"/>
     <n v="3854"/>
-    <n v="5"/>
+    <n v="14"/>
     <n v="0"/>
   </r>
 </pivotCacheRecords>
@@ -2503,12 +2503,12 @@
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A2" s="8" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
     </row>
     <row r="3" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A3" s="9" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.3">
@@ -2634,13 +2634,13 @@
         <v>19</v>
       </c>
       <c r="E9" s="5">
-        <v>609</v>
+        <v>658</v>
       </c>
       <c r="F9" s="5">
-        <v>881</v>
+        <v>948</v>
       </c>
       <c r="G9" s="6">
-        <v>1.4466338259441707</v>
+        <v>1.4407294832826747</v>
       </c>
       <c r="J9">
         <v>2026</v>
@@ -2666,13 +2666,13 @@
         <v>14</v>
       </c>
       <c r="E10" s="5">
-        <v>412</v>
+        <v>471</v>
       </c>
       <c r="F10" s="5">
-        <v>826</v>
+        <v>1039</v>
       </c>
       <c r="G10" s="6">
-        <v>2.0048543689320391</v>
+        <v>2.2059447983014864</v>
       </c>
       <c r="K10">
         <v>2</v>
@@ -2701,13 +2701,13 @@
         <v>19</v>
       </c>
       <c r="E11" s="5">
-        <v>1153</v>
+        <v>1238</v>
       </c>
       <c r="F11" s="5">
-        <v>479</v>
+        <v>540</v>
       </c>
       <c r="G11" s="6">
-        <v>0.41543798785776237</v>
+        <v>0.43618739903069464</v>
       </c>
       <c r="K11">
         <v>3</v>
@@ -2736,13 +2736,13 @@
         <v>14</v>
       </c>
       <c r="E12" s="5">
-        <v>154</v>
+        <v>188</v>
       </c>
       <c r="F12" s="5">
-        <v>922</v>
+        <v>1026</v>
       </c>
       <c r="G12" s="6">
-        <v>5.9870129870129869</v>
+        <v>5.457446808510638</v>
       </c>
       <c r="K12">
         <v>4</v>
@@ -2765,25 +2765,25 @@
         <v>14</v>
       </c>
       <c r="E13" s="5">
-        <v>294</v>
+        <v>302</v>
       </c>
       <c r="F13" s="5">
-        <v>808</v>
+        <v>813</v>
       </c>
       <c r="G13" s="6">
-        <v>2.7482993197278911</v>
+        <v>2.6920529801324502</v>
       </c>
       <c r="K13">
         <v>5</v>
       </c>
       <c r="L13" s="5">
-        <v>721</v>
+        <v>1900</v>
       </c>
       <c r="M13" s="5">
-        <v>2042</v>
+        <v>4175</v>
       </c>
       <c r="N13" s="6">
-        <v>2.8321775312066575</v>
+        <v>2.1973684210526314</v>
       </c>
     </row>
     <row r="14" spans="1:14" x14ac:dyDescent="0.3">
@@ -2800,25 +2800,25 @@
         <v>14</v>
       </c>
       <c r="E14" s="5">
-        <v>94</v>
+        <v>103</v>
       </c>
       <c r="F14" s="5">
         <v>15</v>
       </c>
       <c r="G14" s="6">
-        <v>0.15957446808510639</v>
+        <v>0.14563106796116504</v>
       </c>
       <c r="J14" t="s">
         <v>50</v>
       </c>
       <c r="L14" s="5">
-        <v>11938</v>
+        <v>13117</v>
       </c>
       <c r="M14" s="5">
-        <v>40072</v>
+        <v>42205</v>
       </c>
       <c r="N14" s="6">
-        <v>3.356676160160831</v>
+        <v>3.2175802393840054</v>
       </c>
     </row>
     <row r="15" spans="1:14" x14ac:dyDescent="0.3">
@@ -2829,13 +2829,13 @@
         <v>14</v>
       </c>
       <c r="E15" s="5">
-        <v>104</v>
+        <v>108</v>
       </c>
       <c r="F15" s="5">
         <v>58</v>
       </c>
       <c r="G15" s="6">
-        <v>0.55769230769230771</v>
+        <v>0.53703703703703709</v>
       </c>
     </row>
     <row r="16" spans="1:14" x14ac:dyDescent="0.3">
@@ -2846,13 +2846,13 @@
         <v>14</v>
       </c>
       <c r="E16" s="5">
-        <v>116</v>
+        <v>126</v>
       </c>
       <c r="F16" s="5">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="G16" s="6">
-        <v>0.52586206896551724</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.3">
@@ -2866,13 +2866,13 @@
         <v>45</v>
       </c>
       <c r="E17" s="5">
-        <v>8003</v>
+        <v>8827</v>
       </c>
       <c r="F17" s="5">
-        <v>30926</v>
+        <v>31866</v>
       </c>
       <c r="G17" s="6">
-        <v>3.8643008871673121</v>
+        <v>3.6100600430497338</v>
       </c>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.3">
@@ -2912,13 +2912,13 @@
         <v>14</v>
       </c>
       <c r="E19" s="5">
-        <v>54</v>
+        <v>67</v>
       </c>
       <c r="F19" s="5">
-        <v>320</v>
+        <v>327</v>
       </c>
       <c r="G19" s="6">
-        <v>5.9259259259259256</v>
+        <v>4.8805970149253728</v>
       </c>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.3">
@@ -2929,13 +2929,13 @@
         <v>14</v>
       </c>
       <c r="E20" s="5">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="F20" s="5">
-        <v>147</v>
+        <v>153</v>
       </c>
       <c r="G20" s="6">
-        <v>3.5853658536585367</v>
+        <v>3.558139534883721</v>
       </c>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.3">
@@ -2946,13 +2946,13 @@
         <v>19</v>
       </c>
       <c r="E21" s="5">
-        <v>881</v>
+        <v>956</v>
       </c>
       <c r="F21" s="5">
-        <v>4512</v>
+        <v>5227</v>
       </c>
       <c r="G21" s="6">
-        <v>5.1214528944381383</v>
+        <v>5.4675732217573225</v>
       </c>
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.3">
@@ -2963,13 +2963,13 @@
         <v>14</v>
       </c>
       <c r="E22" s="5">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="F22" s="5">
-        <v>62</v>
+        <v>75</v>
       </c>
       <c r="G22" s="6">
-        <v>4.1333333333333337</v>
+        <v>3.4090909090909092</v>
       </c>
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.3">
@@ -2977,13 +2977,13 @@
         <v>50</v>
       </c>
       <c r="E23" s="5">
-        <v>11938</v>
+        <v>13117</v>
       </c>
       <c r="F23" s="5">
-        <v>40072</v>
+        <v>42205</v>
       </c>
       <c r="G23" s="6">
-        <v>3.356676160160831</v>
+        <v>3.2175802393840054</v>
       </c>
     </row>
   </sheetData>
@@ -3223,10 +3223,10 @@
         <v>3879</v>
       </c>
       <c r="K6" s="1">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="L6" s="1">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="7" spans="1:12" x14ac:dyDescent="0.3">
@@ -3413,7 +3413,7 @@
         <v>3899</v>
       </c>
       <c r="K11" s="1">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="L11" s="1">
         <v>8</v>
@@ -3603,10 +3603,10 @@
         <v>3917</v>
       </c>
       <c r="K16" s="1">
-        <v>27</v>
+        <v>76</v>
       </c>
       <c r="L16" s="1">
-        <v>14</v>
+        <v>81</v>
       </c>
     </row>
     <row r="17" spans="1:12" x14ac:dyDescent="0.3">
@@ -3793,10 +3793,10 @@
         <v>3930</v>
       </c>
       <c r="K21" s="1">
-        <v>6</v>
+        <v>65</v>
       </c>
       <c r="L21" s="1">
-        <v>3</v>
+        <v>216</v>
       </c>
     </row>
     <row r="22" spans="1:12" x14ac:dyDescent="0.3">
@@ -3983,10 +3983,10 @@
         <v>3943</v>
       </c>
       <c r="K26" s="1">
-        <v>71</v>
+        <v>156</v>
       </c>
       <c r="L26" s="1">
-        <v>62</v>
+        <v>123</v>
       </c>
     </row>
     <row r="27" spans="1:12" x14ac:dyDescent="0.3">
@@ -4173,10 +4173,10 @@
         <v>3976</v>
       </c>
       <c r="K31" s="1">
-        <v>27</v>
+        <v>61</v>
       </c>
       <c r="L31" s="1">
-        <v>214</v>
+        <v>318</v>
       </c>
     </row>
     <row r="32" spans="1:12" x14ac:dyDescent="0.3">
@@ -4363,10 +4363,10 @@
         <v>3989</v>
       </c>
       <c r="K36" s="1">
+        <v>17</v>
+      </c>
+      <c r="L36" s="1">
         <v>9</v>
-      </c>
-      <c r="L36" s="1">
-        <v>4</v>
       </c>
     </row>
     <row r="37" spans="1:12" x14ac:dyDescent="0.3">
@@ -4629,10 +4629,10 @@
         <v>4074</v>
       </c>
       <c r="K43" s="1">
-        <v>67</v>
+        <v>142</v>
       </c>
       <c r="L43" s="1">
-        <v>524</v>
+        <v>1239</v>
       </c>
     </row>
     <row r="44" spans="1:12" x14ac:dyDescent="0.3">
@@ -4819,10 +4819,10 @@
         <v>4083</v>
       </c>
       <c r="K48" s="1">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="L48" s="1">
-        <v>0</v>
+        <v>6</v>
       </c>
     </row>
     <row r="49" spans="1:12" x14ac:dyDescent="0.3">
@@ -4971,10 +4971,10 @@
         <v>4090</v>
       </c>
       <c r="K52" s="1">
-        <v>1</v>
+        <v>14</v>
       </c>
       <c r="L52" s="1">
-        <v>14</v>
+        <v>21</v>
       </c>
     </row>
     <row r="53" spans="1:12" x14ac:dyDescent="0.3">
@@ -5161,10 +5161,10 @@
         <v>4128</v>
       </c>
       <c r="K57" s="1">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="L57" s="1">
-        <v>8</v>
+        <v>21</v>
       </c>
     </row>
     <row r="58" spans="1:12" x14ac:dyDescent="0.3">
@@ -5351,10 +5351,10 @@
         <v>3853</v>
       </c>
       <c r="K62" s="1">
-        <v>496</v>
+        <v>1320</v>
       </c>
       <c r="L62" s="1">
-        <v>1191</v>
+        <v>2131</v>
       </c>
     </row>
     <row r="63" spans="1:12" x14ac:dyDescent="0.3">
@@ -5541,7 +5541,7 @@
         <v>3854</v>
       </c>
       <c r="K67" s="1">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="L67" s="1">
         <v>0</v>
